--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 이벤트 데이터 테이블 V1.61.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 이벤트 데이터 테이블 V1.61.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200039\Desktop\작업\. 문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GA7thFinal_Orora\2_Documents\윤태일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE3F0EC-F99F-4A57-8EC8-F7A01C450DEE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7C226A-201E-42E7-B6D9-AA6A163AF25D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17130" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17130" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문서 개요" sheetId="1" r:id="rId1"/>
@@ -4631,7 +4631,7 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13" style="1" customWidth="1"/>
@@ -4640,16 +4640,16 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="85"/>
     </row>
-    <row r="2" spans="1:6" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="5">
         <v>46246</v>
       </c>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B6" s="5">
         <v>46265</v>
       </c>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.45">
       <c r="B7" s="5">
         <v>46266</v>
       </c>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B8" s="5">
         <v>46268</v>
       </c>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="34" x14ac:dyDescent="0.45">
       <c r="B9" s="5">
         <v>46272</v>
       </c>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B10" s="5">
         <v>46279</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B11" s="5">
         <v>46280</v>
       </c>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B12" s="5">
         <v>46288</v>
       </c>
@@ -4786,13 +4786,13 @@
       </c>
       <c r="F12" s="5"/>
     </row>
-    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:6" ht="200.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="200.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="148" t="s">
         <v>22</v>
       </c>
@@ -4801,13 +4801,13 @@
       <c r="E15" s="149"/>
       <c r="F15" s="149"/>
     </row>
-    <row r="17" spans="1:6" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:6" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="174" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2"/>
       <c r="B18" s="148" t="s">
         <v>24</v>
@@ -4817,19 +4817,19 @@
       <c r="E18" s="149"/>
       <c r="F18" s="149"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="257.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="257.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
       <c r="B21" s="148" t="s">
         <v>26</v>
@@ -4839,13 +4839,13 @@
       <c r="E21" s="149"/>
       <c r="F21" s="149"/>
     </row>
-    <row r="23" spans="1:6" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="36" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="150" t="s">
         <v>28</v>
       </c>
@@ -4873,7 +4873,7 @@
     <tabColor theme="8" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" style="87" customWidth="1"/>
     <col min="2" max="2" width="21.5" style="87" customWidth="1"/>
@@ -4882,16 +4882,16 @@
     <col min="5" max="5" width="20.5" style="88" customWidth="1"/>
     <col min="6" max="6" width="43.5" style="87" customWidth="1"/>
     <col min="7" max="7" width="28" style="87" customWidth="1"/>
-    <col min="8" max="8" width="18.875" style="87" customWidth="1"/>
-    <col min="9" max="10" width="19.875" style="87" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" style="87" customWidth="1"/>
+    <col min="9" max="10" width="19.83203125" style="87" customWidth="1"/>
     <col min="11" max="11" width="22.75" style="89" customWidth="1"/>
-    <col min="12" max="12" width="30.875" style="87" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" style="87" customWidth="1"/>
     <col min="13" max="13" width="30" style="87" customWidth="1"/>
     <col min="14" max="14" width="39" style="89" customWidth="1"/>
     <col min="15" max="16384" width="9" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="99" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>185</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>186</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="122" t="s">
         <v>393</v>
       </c>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="N3" s="127"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="122" t="s">
         <v>394</v>
       </c>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="N4" s="127"/>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="122" t="s">
         <v>397</v>
       </c>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="N5" s="127"/>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="122" t="s">
         <v>398</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N6" s="127"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="122" t="s">
         <v>400</v>
       </c>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="N7" s="127"/>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="122" t="s">
         <v>401</v>
       </c>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="N8" s="127"/>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="122" t="s">
         <v>403</v>
       </c>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="N9" s="127"/>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="122" t="s">
         <v>404</v>
       </c>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="N10" s="127"/>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="122" t="s">
         <v>406</v>
       </c>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="N11" s="127"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="122" t="s">
         <v>407</v>
       </c>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="N12" s="127"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="134" t="s">
         <v>409</v>
       </c>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="N13" s="108"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="134" t="s">
         <v>410</v>
       </c>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="N14" s="108"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="134" t="s">
         <v>412</v>
       </c>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="N15" s="108"/>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="134" t="s">
         <v>413</v>
       </c>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="N16" s="108"/>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="134" t="s">
         <v>415</v>
       </c>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="N17" s="108"/>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="134" t="s">
         <v>416</v>
       </c>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="N18" s="108"/>
     </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="134" t="s">
         <v>418</v>
       </c>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="N19" s="108"/>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="134" t="s">
         <v>419</v>
       </c>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="N20" s="108"/>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="134" t="s">
         <v>421</v>
       </c>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="N21" s="138"/>
     </row>
-    <row r="22" spans="1:14" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" s="86" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="134" t="s">
         <v>422</v>
       </c>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="N22" s="138"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="79" t="s">
         <v>427</v>
       </c>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="N23" s="127"/>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="79" t="s">
         <v>428</v>
       </c>
@@ -5839,18 +5839,18 @@
     <tabColor theme="8" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="35" style="90" customWidth="1"/>
     <col min="2" max="2" width="35" style="91" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="90" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="90" customWidth="1"/>
     <col min="4" max="4" width="39.5" style="90" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="90" customWidth="1"/>
     <col min="6" max="6" width="46" style="90" customWidth="1"/>
     <col min="7" max="16384" width="9" style="90"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="24" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="24" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
         <v>489</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="24" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" s="24" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="110" t="s">
         <v>240</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="122" t="s">
         <v>442</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="122" t="s">
         <v>445</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="122" t="s">
         <v>443</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="122" t="s">
         <v>446</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="104" t="s">
         <v>447</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F7" s="106"/>
     </row>
-    <row r="8" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="104" t="s">
         <v>449</v>
       </c>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="F8" s="106"/>
     </row>
-    <row r="9" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="104" t="s">
         <v>448</v>
       </c>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="F9" s="106"/>
     </row>
-    <row r="10" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="104" t="s">
         <v>450</v>
       </c>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F10" s="106"/>
     </row>
-    <row r="11" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="122" t="s">
         <v>451</v>
       </c>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="F11" s="124"/>
     </row>
-    <row r="12" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="122" t="s">
         <v>453</v>
       </c>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="F12" s="124"/>
     </row>
-    <row r="13" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="122" t="s">
         <v>452</v>
       </c>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="F13" s="124"/>
     </row>
-    <row r="14" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="122" t="s">
         <v>454</v>
       </c>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="F14" s="124"/>
     </row>
-    <row r="15" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="104" t="s">
         <v>455</v>
       </c>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="F15" s="106"/>
     </row>
-    <row r="16" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="104" t="s">
         <v>457</v>
       </c>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F16" s="106"/>
     </row>
-    <row r="17" spans="1:6" s="24" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="104" t="s">
         <v>456</v>
       </c>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F17" s="106"/>
     </row>
-    <row r="18" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="104" t="s">
         <v>458</v>
       </c>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="F18" s="106"/>
     </row>
-    <row r="19" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="122" t="s">
         <v>459</v>
       </c>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="F19" s="124"/>
     </row>
-    <row r="20" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="122" t="s">
         <v>461</v>
       </c>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F20" s="124"/>
     </row>
-    <row r="21" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="122" t="s">
         <v>460</v>
       </c>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="F21" s="124"/>
     </row>
-    <row r="22" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="125" t="s">
         <v>462</v>
       </c>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="F22" s="124"/>
     </row>
-    <row r="23" spans="1:6" s="24" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" s="24" customFormat="1" ht="34" x14ac:dyDescent="0.45">
       <c r="A23" s="104" t="s">
         <v>463</v>
       </c>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F23" s="106"/>
     </row>
-    <row r="24" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="104" t="s">
         <v>465</v>
       </c>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F24" s="106"/>
     </row>
-    <row r="25" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="104" t="s">
         <v>464</v>
       </c>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="F25" s="106"/>
     </row>
-    <row r="26" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="104" t="s">
         <v>466</v>
       </c>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="F26" s="106"/>
     </row>
-    <row r="27" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="125" t="s">
         <v>467</v>
       </c>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="F27" s="124"/>
     </row>
-    <row r="28" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="125" t="s">
         <v>469</v>
       </c>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F28" s="124"/>
     </row>
-    <row r="29" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="125" t="s">
         <v>468</v>
       </c>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F29" s="124"/>
     </row>
-    <row r="30" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="125" t="s">
         <v>470</v>
       </c>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F30" s="124"/>
     </row>
-    <row r="31" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="104" t="s">
         <v>471</v>
       </c>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F31" s="106"/>
     </row>
-    <row r="32" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="104" t="s">
         <v>473</v>
       </c>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="F32" s="106"/>
     </row>
-    <row r="33" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="104" t="s">
         <v>472</v>
       </c>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="F33" s="106"/>
     </row>
-    <row r="34" spans="1:6" s="24" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A34" s="104" t="s">
         <v>474</v>
       </c>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F34" s="106"/>
     </row>
-    <row r="35" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="125" t="s">
         <v>475</v>
       </c>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F35" s="124"/>
     </row>
-    <row r="36" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="125" t="s">
         <v>477</v>
       </c>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F36" s="124"/>
     </row>
-    <row r="37" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="125" t="s">
         <v>476</v>
       </c>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="F37" s="124"/>
     </row>
-    <row r="38" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="125" t="s">
         <v>478</v>
       </c>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="F38" s="124"/>
     </row>
-    <row r="39" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="104" t="s">
         <v>479</v>
       </c>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="F39" s="106"/>
     </row>
-    <row r="40" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="104" t="s">
         <v>481</v>
       </c>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="F40" s="106"/>
     </row>
-    <row r="41" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="104" t="s">
         <v>480</v>
       </c>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="F41" s="106"/>
     </row>
-    <row r="42" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="104" t="s">
         <v>482</v>
       </c>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F42" s="106"/>
     </row>
-    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="79" t="s">
         <v>484</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="79" t="s">
         <v>487</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="79" t="s">
         <v>485</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="79" t="s">
         <v>488</v>
       </c>
@@ -6788,19 +6788,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="19.08203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="23.25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="33.125" style="10" customWidth="1"/>
-    <col min="6" max="16" width="25.625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="25.625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" style="10" customWidth="1"/>
+    <col min="6" max="16" width="25.58203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="25.58203125" style="9" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>525</v>
       </c>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>528</v>
       </c>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>530</v>
       </c>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>533</v>
       </c>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>536</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="P7" s="13"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>539</v>
       </c>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>542</v>
       </c>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
         <v>545</v>
       </c>
@@ -7250,7 +7250,7 @@
       <c r="P10" s="13"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>548</v>
       </c>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
         <v>551</v>
       </c>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>554</v>
       </c>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>557</v>
       </c>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>560</v>
       </c>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>563</v>
       </c>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>566</v>
       </c>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>569</v>
       </c>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>572</v>
       </c>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>575</v>
       </c>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>578</v>
       </c>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>581</v>
       </c>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>584</v>
       </c>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>587</v>
       </c>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
         <v>590</v>
       </c>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
         <v>593</v>
       </c>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
         <v>596</v>
       </c>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Q27" s="6"/>
     </row>
-    <row r="28" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
         <v>599</v>
       </c>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>602</v>
       </c>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>605</v>
       </c>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>608</v>
       </c>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>611</v>
       </c>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
         <v>614</v>
       </c>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
         <v>617</v>
       </c>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
         <v>620</v>
       </c>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>623</v>
       </c>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A37" s="13" t="s">
         <v>626</v>
       </c>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A38" s="13" t="s">
         <v>629</v>
       </c>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A39" s="13" t="s">
         <v>632</v>
       </c>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A40" s="13" t="s">
         <v>635</v>
       </c>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A41" s="13" t="s">
         <v>638</v>
       </c>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A42" s="13" t="s">
         <v>641</v>
       </c>
@@ -8757,7 +8757,7 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H81"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -8769,7 +8769,7 @@
     <col min="8" max="8" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="163" t="s">
         <v>29</v>
       </c>
@@ -8781,7 +8781,7 @@
       <c r="G1" s="163"/>
       <c r="H1" s="163"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="45"/>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -8791,7 +8791,7 @@
       <c r="G2" s="45"/>
       <c r="H2" s="45"/>
     </row>
-    <row r="3" spans="1:8" s="31" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" s="31" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="164" t="s">
         <v>30</v>
       </c>
@@ -8803,7 +8803,7 @@
       <c r="G3" s="165"/>
       <c r="H3" s="166"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="51" t="s">
         <v>31</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="28.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>47</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="53" t="s">
         <v>53</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="53" t="s">
         <v>59</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="53" t="s">
         <v>64</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="53" t="s">
         <v>5</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="55"/>
       <c r="B11" s="56"/>
       <c r="C11" s="56"/>
@@ -8995,7 +8995,7 @@
       <c r="G11" s="57"/>
       <c r="H11" s="58"/>
     </row>
-    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A12" s="153" t="s">
         <v>70</v>
       </c>
@@ -9007,7 +9007,7 @@
       <c r="G12" s="154"/>
       <c r="H12" s="155"/>
     </row>
-    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="51" t="s">
         <v>31</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="53" t="s">
         <v>71</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="53" t="s">
         <v>76</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="53" t="s">
         <v>81</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="53" t="s">
         <v>86</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="53" t="s">
         <v>91</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="53" t="s">
         <v>96</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="55"/>
       <c r="B20" s="56"/>
       <c r="C20" s="56"/>
@@ -9199,7 +9199,7 @@
       <c r="G20" s="57"/>
       <c r="H20" s="58"/>
     </row>
-    <row r="21" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A21" s="156" t="s">
         <v>101</v>
       </c>
@@ -9211,7 +9211,7 @@
       <c r="G21" s="157"/>
       <c r="H21" s="159"/>
     </row>
-    <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="59" t="s">
         <v>31</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="32" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" s="32" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="53" t="s">
         <v>102</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="53" t="s">
         <v>106</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="53" t="s">
         <v>109</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="53" t="s">
         <v>112</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="53" t="s">
         <v>115</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="55"/>
       <c r="B28" s="56"/>
       <c r="C28" s="56"/>
@@ -9377,7 +9377,7 @@
       <c r="G28" s="57"/>
       <c r="H28" s="58"/>
     </row>
-    <row r="29" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A29" s="153" t="s">
         <v>120</v>
       </c>
@@ -9389,7 +9389,7 @@
       <c r="G29" s="154"/>
       <c r="H29" s="155"/>
     </row>
-    <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="51" t="s">
         <v>31</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="53" t="s">
         <v>39</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="53" t="s">
         <v>115</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="53" t="s">
         <v>125</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="53" t="s">
         <v>130</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="53" t="s">
         <v>134</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="53" t="s">
         <v>137</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="61" t="s">
         <v>141</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="61" t="s">
         <v>145</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="53" t="s">
         <v>149</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="53" t="s">
         <v>152</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="55"/>
       <c r="B41" s="56"/>
       <c r="C41" s="56"/>
@@ -9685,7 +9685,7 @@
       <c r="G41" s="57"/>
       <c r="H41" s="58"/>
     </row>
-    <row r="42" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A42" s="153" t="s">
         <v>156</v>
       </c>
@@ -9697,7 +9697,7 @@
       <c r="G42" s="154"/>
       <c r="H42" s="155"/>
     </row>
-    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="51" t="s">
         <v>31</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="53" t="s">
         <v>109</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="53" t="s">
         <v>159</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="53" t="s">
         <v>164</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="53" t="s">
         <v>167</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="53" t="s">
         <v>170</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="63"/>
       <c r="B49" s="64"/>
       <c r="C49" s="65"/>
@@ -9863,7 +9863,7 @@
       <c r="G49" s="64"/>
       <c r="H49" s="66"/>
     </row>
-    <row r="50" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A50" s="156" t="s">
         <v>174</v>
       </c>
@@ -9875,7 +9875,7 @@
       <c r="G50" s="157"/>
       <c r="H50" s="159"/>
     </row>
-    <row r="51" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="51" t="s">
         <v>31</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="53" t="s">
         <v>175</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="53" t="s">
         <v>180</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="67"/>
       <c r="B54" s="68"/>
       <c r="C54" s="68"/>
@@ -9963,7 +9963,7 @@
       <c r="G54" s="69"/>
       <c r="H54" s="70"/>
     </row>
-    <row r="55" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A55" s="160" t="s">
         <v>184</v>
       </c>
@@ -9975,7 +9975,7 @@
       <c r="G55" s="161"/>
       <c r="H55" s="162"/>
     </row>
-    <row r="56" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="51" t="s">
         <v>31</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="53" t="s">
         <v>185</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="53" t="s">
         <v>39</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="53" t="s">
         <v>191</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
         <v>194</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="53" t="s">
         <v>200</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="28.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="53" t="s">
         <v>205</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="53" t="s">
         <v>210</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="53" t="s">
         <v>91</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="53" t="s">
         <v>215</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="61" t="s">
         <v>218</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="61" t="s">
         <v>223</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="53" t="s">
         <v>228</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="28.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="28.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="53" t="s">
         <v>233</v>
       </c>
@@ -10339,7 +10339,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="67"/>
       <c r="B70" s="68"/>
       <c r="C70" s="68"/>
@@ -10349,7 +10349,7 @@
       <c r="G70" s="69"/>
       <c r="H70" s="70"/>
     </row>
-    <row r="71" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="A71" s="160" t="s">
         <v>238</v>
       </c>
@@ -10361,7 +10361,7 @@
       <c r="G71" s="161"/>
       <c r="H71" s="162"/>
     </row>
-    <row r="72" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="51" t="s">
         <v>31</v>
       </c>
@@ -10387,7 +10387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="53" t="s">
         <v>239</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="53" t="s">
         <v>243</v>
       </c>
@@ -10439,7 +10439,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="53" t="s">
         <v>246</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="61" t="s">
         <v>251</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="61" t="s">
         <v>256</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="61" t="s">
         <v>5</v>
       </c>
@@ -10543,7 +10543,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="72"/>
       <c r="B79" s="73"/>
       <c r="C79" s="73"/>
@@ -10553,7 +10553,7 @@
       <c r="G79" s="74"/>
       <c r="H79" s="75"/>
     </row>
-    <row r="80" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="41"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -10563,7 +10563,7 @@
       <c r="G80" s="40"/>
       <c r="H80" s="40"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="42"/>
       <c r="B81" s="43"/>
       <c r="C81" s="43"/>
@@ -10596,20 +10596,20 @@
     <tabColor theme="9" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="6" customWidth="1"/>
     <col min="3" max="3" width="23" style="6" customWidth="1"/>
-    <col min="4" max="6" width="33.125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="32.625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="33.125" style="10" customWidth="1"/>
+    <col min="4" max="6" width="33.08203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="32.58203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="33.08203125" style="10" customWidth="1"/>
     <col min="9" max="9" width="24" style="10" customWidth="1"/>
-    <col min="10" max="10" width="25.625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="25.58203125" style="9" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>265</v>
       </c>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>272</v>
       </c>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>279</v>
       </c>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>286</v>
       </c>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="92" t="s">
         <v>293</v>
       </c>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="J7" s="95"/>
     </row>
-    <row r="8" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="92" t="s">
         <v>300</v>
       </c>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="J8" s="99"/>
     </row>
-    <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="92" t="s">
         <v>306</v>
       </c>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="J9" s="99"/>
     </row>
-    <row r="10" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="92" t="s">
         <v>313</v>
       </c>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="J10" s="99"/>
     </row>
-    <row r="11" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="92" t="s">
         <v>320</v>
       </c>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="J11" s="99"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="13"/>
@@ -10955,7 +10955,7 @@
       <c r="I12" s="16"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="13"/>
       <c r="C13" s="13"/>
       <c r="D13" s="16"/>
@@ -10966,7 +10966,7 @@
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="16"/>
@@ -10977,7 +10977,7 @@
       <c r="I14" s="16"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="16"/>
@@ -10988,7 +10988,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="16"/>
@@ -10999,7 +10999,7 @@
       <c r="I16" s="16"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="16"/>
@@ -11010,7 +11010,7 @@
       <c r="I17" s="16"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="16"/>
@@ -11021,7 +11021,7 @@
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="16"/>
@@ -11032,7 +11032,7 @@
       <c r="I19" s="16"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="16"/>
@@ -11043,7 +11043,7 @@
       <c r="I20" s="16"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="16"/>
@@ -11054,7 +11054,7 @@
       <c r="I21" s="16"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="16"/>
@@ -11065,7 +11065,7 @@
       <c r="I22" s="16"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="16"/>
@@ -11076,7 +11076,7 @@
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="16"/>
@@ -11087,7 +11087,7 @@
       <c r="I24" s="16"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="16"/>
@@ -11098,7 +11098,7 @@
       <c r="I25" s="16"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="16"/>
@@ -11109,7 +11109,7 @@
       <c r="I26" s="16"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="16"/>
@@ -11120,7 +11120,7 @@
       <c r="I27" s="16"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="16"/>
@@ -11131,7 +11131,7 @@
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="16"/>
@@ -11142,7 +11142,7 @@
       <c r="I29" s="16"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="16"/>
@@ -11153,7 +11153,7 @@
       <c r="I30" s="16"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="16"/>
@@ -11164,7 +11164,7 @@
       <c r="I31" s="16"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="16"/>
@@ -11175,7 +11175,7 @@
       <c r="I32" s="16"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="16"/>
@@ -11186,7 +11186,7 @@
       <c r="I33" s="16"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="16"/>
@@ -11197,7 +11197,7 @@
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="16"/>
@@ -11208,7 +11208,7 @@
       <c r="I35" s="16"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="16"/>
@@ -11219,7 +11219,7 @@
       <c r="I36" s="16"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="16"/>
@@ -11230,7 +11230,7 @@
       <c r="I37" s="16"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="16"/>
@@ -11241,7 +11241,7 @@
       <c r="I38" s="16"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="16"/>
@@ -11252,7 +11252,7 @@
       <c r="I39" s="16"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="16"/>
@@ -11263,7 +11263,7 @@
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="16"/>
@@ -11274,7 +11274,7 @@
       <c r="I41" s="16"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="16"/>
@@ -11297,26 +11297,26 @@
     <tabColor theme="9" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="24.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="44" style="6" customWidth="1"/>
-    <col min="4" max="4" width="27.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.58203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="28" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="19.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.08203125" style="6" customWidth="1"/>
     <col min="9" max="9" width="23" style="6" customWidth="1"/>
-    <col min="10" max="10" width="33.125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="32.625" style="10" customWidth="1"/>
-    <col min="12" max="14" width="33.125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="33.08203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.58203125" style="10" customWidth="1"/>
+    <col min="12" max="14" width="33.08203125" style="10" customWidth="1"/>
     <col min="15" max="15" width="22.75" style="10" customWidth="1"/>
     <col min="16" max="16" width="26" style="9" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="99" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="102" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" s="33" customFormat="1" ht="32" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="50.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>333</v>
       </c>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P3" s="49"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="18"/>
@@ -11478,7 +11478,7 @@
       <c r="O4" s="16"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="18"/>
@@ -11496,7 +11496,7 @@
       <c r="O5" s="16"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="18"/>
@@ -11514,7 +11514,7 @@
       <c r="O6" s="16"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="18"/>
@@ -11532,7 +11532,7 @@
       <c r="O7" s="16"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="18"/>
@@ -11550,7 +11550,7 @@
       <c r="O8" s="16"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="18"/>
@@ -11568,7 +11568,7 @@
       <c r="O9" s="16"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="18"/>
@@ -11586,7 +11586,7 @@
       <c r="O10" s="16"/>
       <c r="P10" s="6"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="18"/>
@@ -11604,7 +11604,7 @@
       <c r="O11" s="16"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="18"/>
@@ -11622,7 +11622,7 @@
       <c r="O12" s="16"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" s="13"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -11639,7 +11639,7 @@
       <c r="O13" s="16"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" s="13"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -11656,7 +11656,7 @@
       <c r="O14" s="16"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" s="13"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -11673,7 +11673,7 @@
       <c r="O15" s="16"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" s="13"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -11690,7 +11690,7 @@
       <c r="O16" s="16"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17" s="13"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -11707,7 +11707,7 @@
       <c r="O17" s="16"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18" s="13"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -11724,7 +11724,7 @@
       <c r="O18" s="16"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="13"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -11741,7 +11741,7 @@
       <c r="O19" s="16"/>
       <c r="P19" s="6"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" s="13"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -11758,7 +11758,7 @@
       <c r="O20" s="16"/>
       <c r="P20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" s="13"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -11775,7 +11775,7 @@
       <c r="O21" s="16"/>
       <c r="P21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" s="13"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -11804,16 +11804,16 @@
     <tabColor theme="9" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="27.125" style="6" customWidth="1"/>
-    <col min="3" max="10" width="25.625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="52.625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="6" customWidth="1"/>
+    <col min="3" max="10" width="25.58203125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="52.58203125" style="10" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="51" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="33" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="33" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>265</v>
       </c>
@@ -11903,7 +11903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>272</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>279</v>
       </c>
@@ -11951,7 +11951,7 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
     </row>
-    <row r="6" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>286</v>
       </c>
@@ -11976,7 +11976,7 @@
       <c r="J6" s="114"/>
       <c r="K6" s="116"/>
     </row>
-    <row r="7" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="92" t="s">
         <v>293</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="92" t="s">
         <v>300</v>
       </c>
@@ -12032,7 +12032,7 @@
       <c r="J8" s="97"/>
       <c r="K8" s="100"/>
     </row>
-    <row r="9" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="92" t="s">
         <v>306</v>
       </c>
@@ -12057,7 +12057,7 @@
       <c r="J9" s="97"/>
       <c r="K9" s="100"/>
     </row>
-    <row r="10" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="92" t="s">
         <v>313</v>
       </c>
@@ -12082,7 +12082,7 @@
       <c r="J10" s="97"/>
       <c r="K10" s="100"/>
     </row>
-    <row r="11" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="92" t="s">
         <v>320</v>
       </c>
@@ -12107,7 +12107,7 @@
       <c r="J11" s="97"/>
       <c r="K11" s="100"/>
     </row>
-    <row r="12" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
         <v>333</v>
       </c>
@@ -12129,7 +12129,7 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
     </row>
-    <row r="13" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="13"/>
@@ -12141,7 +12141,7 @@
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="13"/>
@@ -12153,7 +12153,7 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="13"/>
@@ -12165,7 +12165,7 @@
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="13"/>
@@ -12177,7 +12177,7 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="13"/>
@@ -12189,7 +12189,7 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="13"/>
@@ -12201,7 +12201,7 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="13"/>
@@ -12213,7 +12213,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="13"/>
@@ -12225,7 +12225,7 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="13"/>
@@ -12237,7 +12237,7 @@
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
     </row>
-    <row r="22" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="13"/>
@@ -12249,7 +12249,7 @@
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="13"/>
@@ -12261,7 +12261,7 @@
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
     </row>
-    <row r="24" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="13"/>
@@ -12273,7 +12273,7 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
     </row>
-    <row r="25" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="13"/>
@@ -12285,7 +12285,7 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="13"/>
@@ -12297,7 +12297,7 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="13"/>
@@ -12309,7 +12309,7 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
     </row>
-    <row r="28" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="13"/>
@@ -12321,7 +12321,7 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="13"/>
@@ -12333,7 +12333,7 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="13"/>
@@ -12345,7 +12345,7 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="13"/>
@@ -12357,7 +12357,7 @@
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
     </row>
-    <row r="32" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="13"/>
@@ -12369,7 +12369,7 @@
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
     </row>
-    <row r="33" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="13"/>
@@ -12381,7 +12381,7 @@
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
     </row>
-    <row r="34" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="13"/>
@@ -12393,7 +12393,7 @@
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
     </row>
-    <row r="35" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="13"/>
@@ -12405,7 +12405,7 @@
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
     </row>
-    <row r="36" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="13"/>
@@ -12417,7 +12417,7 @@
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
     </row>
-    <row r="37" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="13"/>
@@ -12429,7 +12429,7 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
     </row>
-    <row r="38" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="13"/>
@@ -12441,7 +12441,7 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
     </row>
-    <row r="39" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="13"/>
@@ -12453,7 +12453,7 @@
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
     </row>
-    <row r="40" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="13"/>
@@ -12477,22 +12477,22 @@
     <tabColor theme="7" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:K43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.25" style="6" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="6" customWidth="1"/>
     <col min="3" max="3" width="23.25" style="6" customWidth="1"/>
-    <col min="4" max="4" width="33.125" style="35" customWidth="1"/>
-    <col min="5" max="5" width="33.125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="32.625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="25.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="33.08203125" style="35" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.58203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="25.58203125" style="6" customWidth="1"/>
     <col min="8" max="8" width="24" style="6" customWidth="1"/>
-    <col min="9" max="10" width="25.625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="25.625" style="9" customWidth="1"/>
+    <col min="9" max="10" width="25.58203125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="25.58203125" style="9" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>352</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>353</v>
@@ -12591,7 +12591,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>356</v>
       </c>
@@ -12620,7 +12620,7 @@
       <c r="J4" s="82"/>
       <c r="K4" s="84"/>
     </row>
-    <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>360</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>361</v>
@@ -12649,7 +12649,7 @@
       <c r="J5" s="13"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" s="92" t="s">
         <v>364</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="102" t="s">
         <v>365</v>
@@ -12678,7 +12678,7 @@
       <c r="J6" s="93"/>
       <c r="K6" s="95"/>
     </row>
-    <row r="7" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A7" s="92" t="s">
         <v>368</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="103" t="s">
         <v>369</v>
@@ -12707,7 +12707,7 @@
       <c r="J7" s="97"/>
       <c r="K7" s="99"/>
     </row>
-    <row r="8" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="92" t="s">
         <v>372</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="103" t="s">
         <v>373</v>
@@ -12736,7 +12736,7 @@
       <c r="J8" s="97"/>
       <c r="K8" s="99"/>
     </row>
-    <row r="9" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" s="92" t="s">
         <v>376</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="103" t="s">
         <v>377</v>
@@ -12765,7 +12765,7 @@
       <c r="J9" s="97"/>
       <c r="K9" s="99"/>
     </row>
-    <row r="10" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="51" x14ac:dyDescent="0.45">
       <c r="A10" s="92" t="s">
         <v>380</v>
       </c>
@@ -12773,7 +12773,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="103" t="s">
         <v>381</v>
@@ -12794,7 +12794,7 @@
       <c r="J10" s="97"/>
       <c r="K10" s="99"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="13"/>
@@ -12807,7 +12807,7 @@
       <c r="J11" s="13"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="13"/>
@@ -12820,7 +12820,7 @@
       <c r="J12" s="13"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="13"/>
@@ -12833,7 +12833,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="34"/>
@@ -12845,7 +12845,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="34"/>
@@ -12857,7 +12857,7 @@
       <c r="J15" s="13"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="34"/>
@@ -12869,7 +12869,7 @@
       <c r="J16" s="13"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="34"/>
@@ -12881,7 +12881,7 @@
       <c r="J17" s="13"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="34"/>
@@ -12893,7 +12893,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="34"/>
@@ -12905,7 +12905,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="34"/>
@@ -12917,7 +12917,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="34"/>
@@ -12929,7 +12929,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="34"/>
@@ -12941,7 +12941,7 @@
       <c r="J22" s="13"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="34"/>
@@ -12953,7 +12953,7 @@
       <c r="J23" s="13"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="34"/>
@@ -12964,7 +12964,7 @@
       <c r="J24" s="13"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="34"/>
@@ -12975,7 +12975,7 @@
       <c r="J25" s="13"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="34"/>
@@ -12986,7 +12986,7 @@
       <c r="J26" s="13"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="34"/>
@@ -12997,7 +12997,7 @@
       <c r="J27" s="13"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="34"/>
@@ -13008,7 +13008,7 @@
       <c r="J28" s="13"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="34"/>
@@ -13019,7 +13019,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="34"/>
@@ -13030,7 +13030,7 @@
       <c r="J30" s="13"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="34"/>
@@ -13041,7 +13041,7 @@
       <c r="J31" s="13"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="34"/>
@@ -13052,7 +13052,7 @@
       <c r="J32" s="13"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="34"/>
@@ -13063,7 +13063,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="34"/>
@@ -13074,7 +13074,7 @@
       <c r="J34" s="13"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="34"/>
@@ -13085,7 +13085,7 @@
       <c r="J35" s="13"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="34"/>
@@ -13096,7 +13096,7 @@
       <c r="J36" s="13"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="34"/>
@@ -13107,7 +13107,7 @@
       <c r="J37" s="13"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="34"/>
@@ -13118,7 +13118,7 @@
       <c r="J38" s="13"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="34"/>
@@ -13129,7 +13129,7 @@
       <c r="J39" s="13"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="34"/>
@@ -13140,7 +13140,7 @@
       <c r="J40" s="13"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="34"/>
@@ -13151,7 +13151,7 @@
       <c r="J41" s="13"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="34"/>
@@ -13162,7 +13162,7 @@
       <c r="J42" s="13"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="34"/>
@@ -13176,6 +13176,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13185,30 +13186,30 @@
     <tabColor theme="7" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="24.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="44" style="6" customWidth="1"/>
-    <col min="4" max="4" width="27.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.58203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="28" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="6" customWidth="1"/>
     <col min="8" max="8" width="18" style="17" customWidth="1"/>
     <col min="9" max="9" width="17.25" style="17" customWidth="1"/>
     <col min="10" max="10" width="32" style="6" customWidth="1"/>
-    <col min="11" max="11" width="32.625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="32.58203125" style="10" customWidth="1"/>
     <col min="12" max="12" width="28.75" style="35" customWidth="1"/>
     <col min="13" max="13" width="18" style="6" customWidth="1"/>
-    <col min="14" max="14" width="20.625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="25.875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="23.125" style="17" customWidth="1"/>
+    <col min="14" max="14" width="20.58203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="25.83203125" style="6" customWidth="1"/>
+    <col min="16" max="16" width="23.08203125" style="17" customWidth="1"/>
     <col min="17" max="17" width="26" style="17" customWidth="1"/>
-    <col min="18" max="18" width="25.625" style="46" customWidth="1"/>
+    <col min="18" max="18" width="25.58203125" style="46" customWidth="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="48" customFormat="1" ht="99" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="48" customFormat="1" ht="102" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>39</v>
       </c>
@@ -13262,7 +13263,7 @@
       </c>
       <c r="R1" s="47"/>
     </row>
-    <row r="2" spans="1:18" ht="27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>40</v>
       </c>
@@ -13315,7 +13316,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="50.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>385</v>
       </c>
@@ -13362,7 +13363,7 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="50"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="18"/>
@@ -13381,7 +13382,7 @@
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="18"/>
@@ -13400,7 +13401,7 @@
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="18"/>
@@ -13419,7 +13420,7 @@
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="18"/>
@@ -13438,7 +13439,7 @@
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="18"/>
@@ -13457,7 +13458,7 @@
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="18"/>
@@ -13476,7 +13477,7 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="18"/>
@@ -13495,7 +13496,7 @@
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="18"/>
@@ -13514,7 +13515,7 @@
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="18"/>
@@ -13533,7 +13534,7 @@
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13" s="13"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -13551,7 +13552,7 @@
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14" s="13"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -13569,7 +13570,7 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15" s="13"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -13587,7 +13588,7 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16" s="13"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -13605,7 +13606,7 @@
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="13"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -13623,7 +13624,7 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="13"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -13641,7 +13642,7 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="13"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -13659,7 +13660,7 @@
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="13"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -13677,7 +13678,7 @@
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="13"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -13695,7 +13696,7 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="13"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -13725,19 +13726,19 @@
     <tabColor theme="8" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.5" style="87" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="87" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="87" customWidth="1"/>
     <col min="3" max="3" width="23" style="87" customWidth="1"/>
-    <col min="4" max="4" width="28.875" style="88" customWidth="1"/>
-    <col min="5" max="5" width="33.125" style="88" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" style="88" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" style="88" customWidth="1"/>
     <col min="6" max="8" width="24" style="89" customWidth="1"/>
     <col min="9" max="9" width="17.75" style="89" customWidth="1"/>
     <col min="10" max="16384" width="9" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="36" t="s">
         <v>39</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="120" t="s">
         <v>40</v>
       </c>
@@ -13795,7 +13796,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="79" t="s">
         <v>390</v>
       </c>
@@ -13822,7 +13823,7 @@
       </c>
       <c r="I3" s="23"/>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="79" t="s">
         <v>396</v>
       </c>
@@ -13845,7 +13846,7 @@
       <c r="H4" s="19"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.45">
       <c r="A5" s="79" t="s">
         <v>399</v>
       </c>
@@ -13868,7 +13869,7 @@
       <c r="H5" s="19"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="79" t="s">
         <v>402</v>
       </c>
@@ -13891,7 +13892,7 @@
       <c r="H6" s="19"/>
       <c r="I6" s="23"/>
     </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="79" t="s">
         <v>405</v>
       </c>
@@ -13914,7 +13915,7 @@
       <c r="H7" s="19"/>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="105" t="s">
         <v>408</v>
       </c>
@@ -13937,7 +13938,7 @@
       <c r="H8" s="106"/>
       <c r="I8" s="104"/>
     </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="105" t="s">
         <v>411</v>
       </c>
@@ -13960,7 +13961,7 @@
       <c r="H9" s="106"/>
       <c r="I9" s="104"/>
     </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="105" t="s">
         <v>414</v>
       </c>
@@ -13983,7 +13984,7 @@
       <c r="H10" s="106"/>
       <c r="I10" s="104"/>
     </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" s="105" t="s">
         <v>417</v>
       </c>
@@ -14006,7 +14007,7 @@
       <c r="H11" s="106"/>
       <c r="I11" s="104"/>
     </row>
-    <row r="12" spans="1:9" s="86" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="86" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="105" t="s">
         <v>420</v>
       </c>
@@ -14029,7 +14030,7 @@
       <c r="H12" s="106"/>
       <c r="I12" s="104"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="117"/>
       <c r="C13" s="118"/>
       <c r="D13" s="119"/>
@@ -14039,7 +14040,7 @@
       <c r="H13" s="119"/>
       <c r="I13" s="87"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="117"/>
       <c r="C14" s="118"/>
       <c r="D14" s="119"/>
@@ -14049,7 +14050,7 @@
       <c r="H14" s="119"/>
       <c r="I14" s="87"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="117"/>
       <c r="C15" s="118"/>
       <c r="D15" s="119"/>
@@ -14059,7 +14060,7 @@
       <c r="H15" s="119"/>
       <c r="I15" s="87"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="117"/>
       <c r="C16" s="118"/>
       <c r="D16" s="119"/>
@@ -14069,7 +14070,7 @@
       <c r="H16" s="119"/>
       <c r="I16" s="87"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="117"/>
       <c r="C17" s="118"/>
       <c r="D17" s="119"/>
@@ -14079,7 +14080,7 @@
       <c r="H17" s="119"/>
       <c r="I17" s="87"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="117"/>
       <c r="C18" s="118"/>
       <c r="D18" s="119"/>
@@ -14089,7 +14090,7 @@
       <c r="H18" s="119"/>
       <c r="I18" s="87"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="117"/>
       <c r="C19" s="118"/>
       <c r="D19" s="119"/>
@@ -14099,7 +14100,7 @@
       <c r="H19" s="119"/>
       <c r="I19" s="87"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="117"/>
       <c r="C20" s="118"/>
       <c r="D20" s="119"/>
@@ -14109,7 +14110,7 @@
       <c r="H20" s="119"/>
       <c r="I20" s="87"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="117"/>
       <c r="C21" s="118"/>
       <c r="D21" s="119"/>
@@ -14119,7 +14120,7 @@
       <c r="H21" s="119"/>
       <c r="I21" s="87"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="117"/>
       <c r="C22" s="118"/>
       <c r="D22" s="119"/>
@@ -14129,7 +14130,7 @@
       <c r="H22" s="119"/>
       <c r="I22" s="87"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="117"/>
       <c r="C23" s="118"/>
       <c r="D23" s="119"/>
@@ -14139,7 +14140,7 @@
       <c r="H23" s="119"/>
       <c r="I23" s="87"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="117"/>
       <c r="C24" s="118"/>
       <c r="D24" s="119"/>
@@ -14149,7 +14150,7 @@
       <c r="H24" s="119"/>
       <c r="I24" s="87"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="117"/>
       <c r="C25" s="118"/>
       <c r="D25" s="119"/>
@@ -14159,7 +14160,7 @@
       <c r="H25" s="119"/>
       <c r="I25" s="87"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="117"/>
       <c r="C26" s="118"/>
       <c r="D26" s="119"/>
@@ -14169,7 +14170,7 @@
       <c r="H26" s="119"/>
       <c r="I26" s="87"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="117"/>
       <c r="C27" s="118"/>
       <c r="D27" s="119"/>
@@ -14179,7 +14180,7 @@
       <c r="H27" s="119"/>
       <c r="I27" s="87"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="117"/>
       <c r="C28" s="118"/>
       <c r="D28" s="119"/>
@@ -14189,7 +14190,7 @@
       <c r="H28" s="119"/>
       <c r="I28" s="87"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="117"/>
       <c r="C29" s="118"/>
       <c r="D29" s="119"/>
@@ -14199,7 +14200,7 @@
       <c r="H29" s="119"/>
       <c r="I29" s="87"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="117"/>
       <c r="C30" s="118"/>
       <c r="D30" s="119"/>
@@ -14209,7 +14210,7 @@
       <c r="H30" s="119"/>
       <c r="I30" s="87"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="117"/>
       <c r="C31" s="118"/>
       <c r="D31" s="119"/>
@@ -14219,7 +14220,7 @@
       <c r="H31" s="119"/>
       <c r="I31" s="87"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="117"/>
       <c r="C32" s="118"/>
       <c r="D32" s="119"/>
@@ -14229,7 +14230,7 @@
       <c r="H32" s="119"/>
       <c r="I32" s="87"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="117"/>
       <c r="C33" s="118"/>
       <c r="D33" s="119"/>
@@ -14239,7 +14240,7 @@
       <c r="H33" s="119"/>
       <c r="I33" s="87"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="117"/>
       <c r="C34" s="118"/>
       <c r="D34" s="119"/>
@@ -14249,7 +14250,7 @@
       <c r="H34" s="119"/>
       <c r="I34" s="87"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="117"/>
       <c r="C35" s="118"/>
       <c r="D35" s="119"/>
@@ -14259,7 +14260,7 @@
       <c r="H35" s="119"/>
       <c r="I35" s="87"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="117"/>
       <c r="C36" s="118"/>
       <c r="D36" s="119"/>
@@ -14269,7 +14270,7 @@
       <c r="H36" s="119"/>
       <c r="I36" s="87"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="117"/>
       <c r="C37" s="118"/>
       <c r="D37" s="119"/>
@@ -14279,7 +14280,7 @@
       <c r="H37" s="119"/>
       <c r="I37" s="87"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="117"/>
       <c r="C38" s="118"/>
       <c r="D38" s="119"/>
@@ -14289,7 +14290,7 @@
       <c r="H38" s="119"/>
       <c r="I38" s="87"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="117"/>
       <c r="C39" s="118"/>
       <c r="D39" s="119"/>
@@ -14299,7 +14300,7 @@
       <c r="H39" s="119"/>
       <c r="I39" s="87"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="117"/>
       <c r="C40" s="118"/>
       <c r="D40" s="119"/>
@@ -14309,7 +14310,7 @@
       <c r="H40" s="119"/>
       <c r="I40" s="87"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="117"/>
       <c r="C41" s="118"/>
       <c r="D41" s="119"/>
@@ -14319,7 +14320,7 @@
       <c r="H41" s="119"/>
       <c r="I41" s="87"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="117"/>
       <c r="C42" s="118"/>
       <c r="D42" s="119"/>
@@ -14380,27 +14381,27 @@
     <tabColor theme="8" tint="0.59974974822229687"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="24.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="44" style="6" customWidth="1"/>
-    <col min="4" max="4" width="27.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.58203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="28" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="6" customWidth="1"/>
     <col min="8" max="8" width="18" style="6" customWidth="1"/>
     <col min="9" max="9" width="14.75" style="6" customWidth="1"/>
     <col min="10" max="10" width="32" style="6" customWidth="1"/>
-    <col min="11" max="11" width="33.125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="24.875" style="10" customWidth="1"/>
-    <col min="13" max="13" width="24.875" style="17" customWidth="1"/>
+    <col min="11" max="11" width="33.08203125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" style="17" customWidth="1"/>
     <col min="14" max="14" width="24" style="17" customWidth="1"/>
     <col min="15" max="15" width="26" style="17" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="102" x14ac:dyDescent="0.45">
       <c r="A1" s="77" t="s">
         <v>39</v>
       </c>
@@ -14447,7 +14448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="78" t="s">
         <v>40</v>
       </c>
@@ -14494,7 +14495,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="50.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="79" t="s">
         <v>423</v>
       </c>
@@ -14535,7 +14536,7 @@
       </c>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="79"/>
       <c r="B4" s="8"/>
       <c r="C4" s="18"/>
@@ -14552,7 +14553,7 @@
       <c r="N4" s="19"/>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="79"/>
       <c r="B5" s="8"/>
       <c r="C5" s="18"/>
@@ -14569,7 +14570,7 @@
       <c r="N5" s="19"/>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="79"/>
       <c r="B6" s="8"/>
       <c r="C6" s="18"/>
@@ -14586,7 +14587,7 @@
       <c r="N6" s="19"/>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="79"/>
       <c r="B7" s="8"/>
       <c r="C7" s="18"/>
@@ -14603,7 +14604,7 @@
       <c r="N7" s="19"/>
       <c r="O7" s="19"/>
     </row>
-    <row r="8" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="79"/>
       <c r="B8" s="8"/>
       <c r="C8" s="18"/>
@@ -14620,7 +14621,7 @@
       <c r="N8" s="19"/>
       <c r="O8" s="19"/>
     </row>
-    <row r="9" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="79"/>
       <c r="B9" s="8"/>
       <c r="C9" s="18"/>
@@ -14637,7 +14638,7 @@
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
     </row>
-    <row r="10" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="79"/>
       <c r="B10" s="8"/>
       <c r="C10" s="18"/>
@@ -14654,7 +14655,7 @@
       <c r="N10" s="19"/>
       <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="79"/>
       <c r="B11" s="8"/>
       <c r="C11" s="18"/>
@@ -14671,7 +14672,7 @@
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
     </row>
-    <row r="12" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="79"/>
       <c r="B12" s="8"/>
       <c r="C12" s="18"/>
@@ -14688,7 +14689,7 @@
       <c r="N12" s="19"/>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="37"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -14704,7 +14705,7 @@
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="37"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -14720,7 +14721,7 @@
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="37"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -14736,7 +14737,7 @@
       <c r="N15" s="16"/>
       <c r="O15" s="16"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="37"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -14752,7 +14753,7 @@
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="37"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -14768,7 +14769,7 @@
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="37"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -14784,7 +14785,7 @@
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="37"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -14800,7 +14801,7 @@
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="37"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -14816,7 +14817,7 @@
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="37"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -14832,7 +14833,7 @@
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="37"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -14848,83 +14849,83 @@
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K23" s="16"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K24" s="16"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K25" s="16"/>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K26" s="16"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K40" s="16"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="11:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="11:14" x14ac:dyDescent="0.45">
       <c r="K42" s="16"/>
       <c r="N42" s="16"/>
     </row>
